--- a/Masters_Scores.xlsx
+++ b/Masters_Scores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasgwartz/Desktop/Job/Projects/Python/Masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24CF582-D535-F546-8B7E-B2AD2CE93A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE071A1-7C16-F144-82FA-4E4D15F3C905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="15900" xr2:uid="{67E4DBFB-4AA8-0A4F-A49D-EE0116D15928}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="12560" windowHeight="15980" xr2:uid="{67E4DBFB-4AA8-0A4F-A49D-EE0116D15928}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
   <si>
     <t>Horton Smith</t>
   </si>
@@ -361,16 +361,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -687,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ADD9961-473D-E04F-B264-B4AF03F2105D}">
-  <dimension ref="A1:V90"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="4"/>
@@ -703,56 +703,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
       <c r="V1" s="1"/>
     </row>
     <row r="2" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -811,8 +811,8 @@
         <f t="shared" ref="P2:P33" si="6">O2-72</f>
         <v>0</v>
       </c>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
       <c r="V2" s="2"/>
     </row>
     <row r="3" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -871,8 +871,8 @@
         <f t="shared" si="6"/>
         <v>-2</v>
       </c>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
       <c r="V3" s="2"/>
     </row>
     <row r="4" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -931,8 +931,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
       <c r="V4" s="2"/>
     </row>
     <row r="5" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -991,8 +991,8 @@
         <f t="shared" si="6"/>
         <v>-2</v>
       </c>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
       <c r="V5" s="2"/>
     </row>
     <row r="6" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1051,8 +1051,8 @@
         <f t="shared" si="6"/>
         <v>-2</v>
       </c>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
       <c r="V6" s="2"/>
     </row>
     <row r="7" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1111,8 +1111,8 @@
         <f t="shared" si="6"/>
         <v>-3</v>
       </c>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
       <c r="V7" s="2"/>
     </row>
     <row r="8" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1171,8 +1171,8 @@
         <f t="shared" si="6"/>
         <v>-1</v>
       </c>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
       <c r="V8" s="2"/>
     </row>
     <row r="9" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1231,8 +1231,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
       <c r="V9" s="2"/>
     </row>
     <row r="10" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1291,8 +1291,8 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
       <c r="V10" s="2"/>
     </row>
     <row r="11" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1351,8 +1351,8 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
       <c r="V11" s="2"/>
     </row>
     <row r="12" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1411,8 +1411,8 @@
         <f t="shared" si="6"/>
         <v>-1</v>
       </c>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
       <c r="V12" s="2"/>
     </row>
     <row r="13" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1471,8 +1471,8 @@
         <f t="shared" si="6"/>
         <v>-2</v>
       </c>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
       <c r="V13" s="2"/>
     </row>
     <row r="14" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1531,8 +1531,8 @@
         <f t="shared" si="6"/>
         <v>-5</v>
       </c>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
       <c r="V14" s="2"/>
     </row>
     <row r="15" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1591,8 +1591,8 @@
         <f t="shared" si="6"/>
         <v>-3</v>
       </c>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
       <c r="V15" s="2"/>
     </row>
     <row r="16" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1651,8 +1651,8 @@
         <f t="shared" si="6"/>
         <v>-4</v>
       </c>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
       <c r="V16" s="2"/>
     </row>
     <row r="17" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1711,8 +1711,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
       <c r="V17" s="2"/>
     </row>
     <row r="18" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1771,8 +1771,8 @@
         <f t="shared" si="6"/>
         <v>-3</v>
       </c>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
       <c r="V18" s="2"/>
     </row>
     <row r="19" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1831,8 +1831,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
       <c r="V19" s="2"/>
     </row>
     <row r="20" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1891,8 +1891,8 @@
         <f t="shared" si="6"/>
         <v>-2</v>
       </c>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
       <c r="V20" s="2"/>
     </row>
     <row r="21" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -1951,8 +1951,8 @@
         <f t="shared" si="6"/>
         <v>-1</v>
       </c>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
       <c r="V21" s="2"/>
     </row>
     <row r="22" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2011,8 +2011,8 @@
         <f t="shared" si="6"/>
         <v>-6</v>
       </c>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
       <c r="V22" s="2"/>
     </row>
     <row r="23" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2071,8 +2071,8 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
       <c r="V23" s="2"/>
     </row>
     <row r="24" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2131,8 +2131,8 @@
         <f t="shared" si="6"/>
         <v>-6</v>
       </c>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
       <c r="V24" s="2"/>
     </row>
     <row r="25" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2191,8 +2191,8 @@
         <f t="shared" si="6"/>
         <v>-2</v>
       </c>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
       <c r="V25" s="2"/>
     </row>
     <row r="26" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2251,8 +2251,8 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
       <c r="V26" s="2"/>
     </row>
     <row r="27" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2311,8 +2311,8 @@
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
       <c r="V27" s="2"/>
     </row>
     <row r="28" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2371,8 +2371,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
       <c r="V28" s="2"/>
     </row>
     <row r="29" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2431,8 +2431,8 @@
         <f t="shared" si="6"/>
         <v>-2</v>
       </c>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
       <c r="V29" s="2"/>
     </row>
     <row r="30" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2491,8 +2491,8 @@
         <f t="shared" si="6"/>
         <v>-3</v>
       </c>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
       <c r="V30" s="2"/>
     </row>
     <row r="31" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2551,8 +2551,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
       <c r="V31" s="2"/>
     </row>
     <row r="32" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2611,8 +2611,8 @@
         <f t="shared" si="6"/>
         <v>-5</v>
       </c>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
       <c r="V32" s="2"/>
     </row>
     <row r="33" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2671,8 +2671,8 @@
         <f t="shared" si="6"/>
         <v>-6</v>
       </c>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
       <c r="V33" s="2"/>
     </row>
     <row r="34" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2731,8 +2731,8 @@
         <f t="shared" ref="P34:P65" si="13">O34-72</f>
         <v>0</v>
       </c>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
       <c r="V34" s="2"/>
     </row>
     <row r="35" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2791,8 +2791,8 @@
         <f t="shared" si="13"/>
         <v>-1</v>
       </c>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
       <c r="V35" s="2"/>
     </row>
     <row r="36" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2851,8 +2851,8 @@
         <f t="shared" si="13"/>
         <v>-2</v>
       </c>
-      <c r="R36" s="9"/>
-      <c r="S36" s="9"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
       <c r="V36" s="2"/>
     </row>
     <row r="37" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2911,8 +2911,8 @@
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="11"/>
       <c r="V37" s="2"/>
     </row>
     <row r="38" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -2971,8 +2971,8 @@
         <f t="shared" si="13"/>
         <v>-4</v>
       </c>
-      <c r="R38" s="9"/>
-      <c r="S38" s="9"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="11"/>
       <c r="V38" s="2"/>
     </row>
     <row r="39" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3031,8 +3031,8 @@
         <f t="shared" si="13"/>
         <v>-2</v>
       </c>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
       <c r="V39" s="2"/>
     </row>
     <row r="40" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3091,8 +3091,8 @@
         <f t="shared" si="13"/>
         <v>-4</v>
       </c>
-      <c r="R40" s="9"/>
-      <c r="S40" s="9"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
       <c r="V40" s="2"/>
     </row>
     <row r="41" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3151,8 +3151,8 @@
         <f t="shared" si="13"/>
         <v>-2</v>
       </c>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
       <c r="V41" s="2"/>
     </row>
     <row r="42" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3211,8 +3211,8 @@
         <f t="shared" si="13"/>
         <v>-5</v>
       </c>
-      <c r="R42" s="9"/>
-      <c r="S42" s="9"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
       <c r="V42" s="2"/>
     </row>
     <row r="43" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3271,8 +3271,8 @@
         <f t="shared" si="13"/>
         <v>-8</v>
       </c>
-      <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="11"/>
       <c r="V43" s="2"/>
     </row>
     <row r="44" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3331,8 +3331,8 @@
         <f t="shared" si="13"/>
         <v>-2</v>
       </c>
-      <c r="R44" s="9"/>
-      <c r="S44" s="9"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
       <c r="V44" s="2"/>
     </row>
     <row r="45" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3391,8 +3391,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="R45" s="9"/>
-      <c r="S45" s="9"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
       <c r="V45" s="2"/>
     </row>
     <row r="46" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3451,8 +3451,8 @@
         <f t="shared" si="13"/>
         <v>-1</v>
       </c>
-      <c r="R46" s="9"/>
-      <c r="S46" s="9"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
       <c r="V46" s="2"/>
     </row>
     <row r="47" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3511,8 +3511,8 @@
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="R47" s="9"/>
-      <c r="S47" s="9"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="11"/>
       <c r="V47" s="2"/>
     </row>
     <row r="48" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3571,8 +3571,8 @@
         <f t="shared" si="13"/>
         <v>-3</v>
       </c>
-      <c r="R48" s="9"/>
-      <c r="S48" s="9"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="11"/>
       <c r="V48" s="2"/>
     </row>
     <row r="49" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3631,8 +3631,8 @@
         <f t="shared" si="13"/>
         <v>-4</v>
       </c>
-      <c r="R49" s="9"/>
-      <c r="S49" s="9"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
       <c r="V49" s="2"/>
     </row>
     <row r="50" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3691,8 +3691,8 @@
         <f t="shared" si="13"/>
         <v>-4</v>
       </c>
-      <c r="R50" s="9"/>
-      <c r="S50" s="9"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="11"/>
       <c r="V50" s="2"/>
     </row>
     <row r="51" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3751,8 +3751,8 @@
         <f t="shared" si="13"/>
         <v>-7</v>
       </c>
-      <c r="R51" s="9"/>
-      <c r="S51" s="9"/>
+      <c r="R51" s="11"/>
+      <c r="S51" s="11"/>
       <c r="V51" s="2"/>
     </row>
     <row r="52" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3811,8 +3811,8 @@
         <f t="shared" si="13"/>
         <v>-1</v>
       </c>
-      <c r="R52" s="9"/>
-      <c r="S52" s="9"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
       <c r="V52" s="2"/>
     </row>
     <row r="53" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3871,8 +3871,8 @@
         <f t="shared" si="13"/>
         <v>-1</v>
       </c>
-      <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
       <c r="V53" s="2"/>
     </row>
     <row r="54" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3931,8 +3931,8 @@
         <f t="shared" si="13"/>
         <v>-7</v>
       </c>
-      <c r="R54" s="9"/>
-      <c r="S54" s="9"/>
+      <c r="R54" s="11"/>
+      <c r="S54" s="11"/>
       <c r="V54" s="2"/>
     </row>
     <row r="55" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -3991,8 +3991,8 @@
         <f t="shared" si="13"/>
         <v>-3</v>
       </c>
-      <c r="R55" s="9"/>
-      <c r="S55" s="9"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="11"/>
       <c r="V55" s="2"/>
     </row>
     <row r="56" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4051,8 +4051,8 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="R56" s="9"/>
-      <c r="S56" s="9"/>
+      <c r="R56" s="11"/>
+      <c r="S56" s="11"/>
       <c r="V56" s="2"/>
     </row>
     <row r="57" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4111,8 +4111,8 @@
         <f t="shared" si="13"/>
         <v>-2</v>
       </c>
-      <c r="R57" s="9"/>
-      <c r="S57" s="9"/>
+      <c r="R57" s="11"/>
+      <c r="S57" s="11"/>
       <c r="V57" s="2"/>
     </row>
     <row r="58" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4171,8 +4171,8 @@
         <f t="shared" si="13"/>
         <v>-2</v>
       </c>
-      <c r="R58" s="9"/>
-      <c r="S58" s="9"/>
+      <c r="R58" s="11"/>
+      <c r="S58" s="11"/>
       <c r="V58" s="2"/>
     </row>
     <row r="59" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4231,8 +4231,8 @@
         <f t="shared" si="13"/>
         <v>-3</v>
       </c>
-      <c r="R59" s="9"/>
-      <c r="S59" s="9"/>
+      <c r="R59" s="11"/>
+      <c r="S59" s="11"/>
       <c r="V59" s="2"/>
     </row>
     <row r="60" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4291,8 +4291,8 @@
         <f t="shared" si="13"/>
         <v>-4</v>
       </c>
-      <c r="R60" s="9"/>
-      <c r="S60" s="9"/>
+      <c r="R60" s="11"/>
+      <c r="S60" s="11"/>
       <c r="V60" s="2"/>
     </row>
     <row r="61" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4351,8 +4351,8 @@
         <f t="shared" si="13"/>
         <v>-5</v>
       </c>
-      <c r="R61" s="9"/>
-      <c r="S61" s="9"/>
+      <c r="R61" s="11"/>
+      <c r="S61" s="11"/>
       <c r="V61" s="2"/>
     </row>
     <row r="62" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4411,8 +4411,8 @@
         <f t="shared" si="13"/>
         <v>-3</v>
       </c>
-      <c r="R62" s="9"/>
-      <c r="S62" s="9"/>
+      <c r="R62" s="11"/>
+      <c r="S62" s="11"/>
       <c r="V62" s="2"/>
     </row>
     <row r="63" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4471,8 +4471,8 @@
         <f t="shared" si="13"/>
         <v>-5</v>
       </c>
-      <c r="R63" s="9"/>
-      <c r="S63" s="9"/>
+      <c r="R63" s="11"/>
+      <c r="S63" s="11"/>
       <c r="V63" s="2"/>
     </row>
     <row r="64" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4531,8 +4531,8 @@
         <f t="shared" si="13"/>
         <v>-1</v>
       </c>
-      <c r="R64" s="9"/>
-      <c r="S64" s="9"/>
+      <c r="R64" s="11"/>
+      <c r="S64" s="11"/>
       <c r="V64" s="2"/>
     </row>
     <row r="65" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4591,8 +4591,8 @@
         <f t="shared" si="13"/>
         <v>-3</v>
       </c>
-      <c r="R65" s="9"/>
-      <c r="S65" s="9"/>
+      <c r="R65" s="11"/>
+      <c r="S65" s="11"/>
       <c r="V65" s="2"/>
     </row>
     <row r="66" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4623,7 +4623,7 @@
         <v>66</v>
       </c>
       <c r="I66" s="2">
-        <f t="shared" ref="I66:I90" si="16">$H66-72</f>
+        <f t="shared" ref="I66:I91" si="16">$H66-72</f>
         <v>-6</v>
       </c>
       <c r="J66" s="2">
@@ -4637,7 +4637,7 @@
         <v>68</v>
       </c>
       <c r="M66" s="2">
-        <f t="shared" ref="M66:M90" si="18">$L66-72</f>
+        <f t="shared" ref="M66:M91" si="18">$L66-72</f>
         <v>-4</v>
       </c>
       <c r="N66" s="2">
@@ -4648,11 +4648,11 @@
         <v>68</v>
       </c>
       <c r="P66" s="3">
-        <f t="shared" ref="P66:P90" si="20">O66-72</f>
+        <f t="shared" ref="P66:P91" si="20">O66-72</f>
         <v>-4</v>
       </c>
-      <c r="R66" s="9"/>
-      <c r="S66" s="9"/>
+      <c r="R66" s="11"/>
+      <c r="S66" s="11"/>
       <c r="V66" s="2"/>
     </row>
     <row r="67" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4711,8 +4711,8 @@
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="R67" s="9"/>
-      <c r="S67" s="9"/>
+      <c r="R67" s="11"/>
+      <c r="S67" s="11"/>
       <c r="V67" s="2"/>
     </row>
     <row r="68" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4771,8 +4771,8 @@
         <f t="shared" si="20"/>
         <v>-4</v>
       </c>
-      <c r="R68" s="9"/>
-      <c r="S68" s="9"/>
+      <c r="R68" s="11"/>
+      <c r="S68" s="11"/>
       <c r="V68" s="2"/>
     </row>
     <row r="69" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4831,8 +4831,8 @@
         <f t="shared" si="20"/>
         <v>-3</v>
       </c>
-      <c r="R69" s="9"/>
-      <c r="S69" s="9"/>
+      <c r="R69" s="11"/>
+      <c r="S69" s="11"/>
       <c r="V69" s="2"/>
     </row>
     <row r="70" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4891,8 +4891,8 @@
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="R70" s="9"/>
-      <c r="S70" s="9"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
       <c r="V70" s="2"/>
     </row>
     <row r="71" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -4951,8 +4951,8 @@
         <f t="shared" si="20"/>
         <v>-3</v>
       </c>
-      <c r="R71" s="9"/>
-      <c r="S71" s="9"/>
+      <c r="R71" s="11"/>
+      <c r="S71" s="11"/>
       <c r="V71" s="2"/>
     </row>
     <row r="72" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5011,8 +5011,8 @@
         <f t="shared" si="20"/>
         <v>-3</v>
       </c>
-      <c r="R72" s="9"/>
-      <c r="S72" s="9"/>
+      <c r="R72" s="11"/>
+      <c r="S72" s="11"/>
       <c r="V72" s="2"/>
     </row>
     <row r="73" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5071,8 +5071,8 @@
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
-      <c r="R73" s="9"/>
-      <c r="S73" s="9"/>
+      <c r="R73" s="11"/>
+      <c r="S73" s="11"/>
       <c r="V73" s="2"/>
     </row>
     <row r="74" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5131,8 +5131,8 @@
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="R74" s="9"/>
-      <c r="S74" s="9"/>
+      <c r="R74" s="11"/>
+      <c r="S74" s="11"/>
       <c r="V74" s="2"/>
     </row>
     <row r="75" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5191,8 +5191,8 @@
         <f t="shared" si="20"/>
         <v>-5</v>
       </c>
-      <c r="R75" s="9"/>
-      <c r="S75" s="9"/>
+      <c r="R75" s="11"/>
+      <c r="S75" s="11"/>
       <c r="V75" s="2"/>
     </row>
     <row r="76" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5251,8 +5251,8 @@
         <f t="shared" si="20"/>
         <v>-6</v>
       </c>
-      <c r="R76" s="9"/>
-      <c r="S76" s="9"/>
+      <c r="R76" s="11"/>
+      <c r="S76" s="11"/>
       <c r="V76" s="2"/>
     </row>
     <row r="77" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5311,8 +5311,8 @@
         <f t="shared" si="20"/>
         <v>-4</v>
       </c>
-      <c r="R77" s="9"/>
-      <c r="S77" s="9"/>
+      <c r="R77" s="11"/>
+      <c r="S77" s="11"/>
       <c r="V77" s="2"/>
     </row>
     <row r="78" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5371,8 +5371,8 @@
         <f t="shared" si="20"/>
         <v>-3</v>
       </c>
-      <c r="R78" s="9"/>
-      <c r="S78" s="9"/>
+      <c r="R78" s="11"/>
+      <c r="S78" s="11"/>
       <c r="V78" s="2"/>
     </row>
     <row r="79" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5431,8 +5431,8 @@
         <f t="shared" si="20"/>
         <v>-3</v>
       </c>
-      <c r="R79" s="9"/>
-      <c r="S79" s="9"/>
+      <c r="R79" s="11"/>
+      <c r="S79" s="11"/>
       <c r="V79" s="2"/>
     </row>
     <row r="80" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5491,8 +5491,8 @@
         <f t="shared" si="20"/>
         <v>-2</v>
       </c>
-      <c r="R80" s="9"/>
-      <c r="S80" s="9"/>
+      <c r="R80" s="11"/>
+      <c r="S80" s="11"/>
       <c r="V80" s="2"/>
     </row>
     <row r="81" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5551,8 +5551,8 @@
         <f t="shared" si="20"/>
         <v>-5</v>
       </c>
-      <c r="R81" s="9"/>
-      <c r="S81" s="9"/>
+      <c r="R81" s="11"/>
+      <c r="S81" s="11"/>
       <c r="V81" s="2"/>
     </row>
     <row r="82" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5611,8 +5611,8 @@
         <f t="shared" si="20"/>
         <v>-3</v>
       </c>
-      <c r="R82" s="9"/>
-      <c r="S82" s="9"/>
+      <c r="R82" s="11"/>
+      <c r="S82" s="11"/>
       <c r="V82" s="2"/>
     </row>
     <row r="83" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5671,8 +5671,8 @@
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="R83" s="9"/>
-      <c r="S83" s="9"/>
+      <c r="R83" s="11"/>
+      <c r="S83" s="11"/>
       <c r="V83" s="2"/>
     </row>
     <row r="84" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5731,8 +5731,8 @@
         <f t="shared" si="20"/>
         <v>-2</v>
       </c>
-      <c r="R84" s="9"/>
-      <c r="S84" s="9"/>
+      <c r="R84" s="11"/>
+      <c r="S84" s="11"/>
       <c r="V84" s="2"/>
     </row>
     <row r="85" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5791,8 +5791,8 @@
         <f t="shared" si="20"/>
         <v>-4</v>
       </c>
-      <c r="R85" s="9"/>
-      <c r="S85" s="9"/>
+      <c r="R85" s="11"/>
+      <c r="S85" s="11"/>
       <c r="V85" s="2"/>
     </row>
     <row r="86" spans="1:22" ht="20" x14ac:dyDescent="0.2">
@@ -5851,8 +5851,8 @@
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
-      <c r="R86" s="9"/>
-      <c r="S86" s="9"/>
+      <c r="R86" s="11"/>
+      <c r="S86" s="11"/>
       <c r="V86" s="2"/>
     </row>
     <row r="87" spans="1:22" s="6" customFormat="1" ht="21" x14ac:dyDescent="0.25">
@@ -6084,6 +6084,62 @@
       <c r="P90" s="7">
         <f t="shared" si="20"/>
         <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" ht="20" x14ac:dyDescent="0.2">
+      <c r="A91" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C91" s="7">
+        <v>1</v>
+      </c>
+      <c r="D91" s="7">
+        <v>67</v>
+      </c>
+      <c r="E91" s="7">
+        <f>$D91-72</f>
+        <v>-5</v>
+      </c>
+      <c r="F91" s="7">
+        <f>SUM(D91+H91)</f>
+        <v>132</v>
+      </c>
+      <c r="G91" s="7">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7">
+        <v>65</v>
+      </c>
+      <c r="I91" s="7">
+        <f t="shared" si="16"/>
+        <v>-7</v>
+      </c>
+      <c r="J91" s="7">
+        <f>F91+H91</f>
+        <v>197</v>
+      </c>
+      <c r="K91" s="7">
+        <v>2</v>
+      </c>
+      <c r="L91" s="7">
+        <v>73</v>
+      </c>
+      <c r="M91" s="7">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="N91" s="7">
+        <v>276</v>
+      </c>
+      <c r="O91" s="7">
+        <v>71</v>
+      </c>
+      <c r="P91" s="7">
+        <f t="shared" si="20"/>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
